--- a/数据表/Datas/FormatText_格式化文本.xlsx
+++ b/数据表/Datas/FormatText_格式化文本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>{0} ITEMS   /   {1} TOTAL UNITS</t>
+  </si>
+  <si>
+    <t>BattleBarText</t>
+  </si>
+  <si>
+    <t>{0} / {1}</t>
   </si>
 </sst>
 </file>
@@ -1359,7 +1365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="13.5955882352941" style="2" customWidth="1"/>
@@ -1476,6 +1482,14 @@
         <v>23</v>
       </c>
     </row>
+    <row r="12" customHeight="1" spans="1:4">
+      <c r="B12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
